--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_277_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_277_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8985</v>
+        <v>7.539</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5995</v>
+        <v>7.3072</v>
       </c>
       <c r="F2" t="n">
-        <v>0.299</v>
+        <v>0.2318</v>
       </c>
       <c r="G2" t="n">
         <v>5.4208</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0789</v>
+        <v>-0.4384</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7389</v>
+        <v>-0.0312</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.34</v>
+        <v>-0.4072</v>
       </c>
       <c r="V2" t="n">
         <v>1.8608</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5288</v>
+        <v>4.1015</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8184</v>
+        <v>3.2902</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7104</v>
+        <v>0.8112</v>
       </c>
       <c r="G3" t="n">
         <v>0.7326</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3482</v>
+        <v>-0.7756</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.4259</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6953</v>
+        <v>2.3415</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4372</v>
+        <v>1.0834</v>
       </c>
       <c r="F4" t="n">
         <v>1.2581</v>
@@ -766,10 +766,10 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>0.456</v>
+        <v>0.1021</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7943</v>
+        <v>0.4404</v>
       </c>
       <c r="U4" t="n">
         <v>-0.3383</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1184</v>
+        <v>1.3146</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2533</v>
+        <v>0.4453</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8651</v>
+        <v>0.8693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3173</v>
+        <v>-0.1294</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2509</v>
+        <v>1.3428</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9336</v>
+        <v>-1.4722</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4636</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3935</v>
+        <v>0.6966</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0701</v>
+        <v>0.2676</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1463</v>
+        <v>-1.0936</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.6462</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0037</v>
+        <v>-1.7398</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0391</v>
+        <v>0.0187</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0351</v>
+        <v>0.3031</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0039</v>
+        <v>-0.2844</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.9615</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1444</v>
+        <v>1.4975</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>N. NEDOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9855</v>
+        <v>1.1142</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0452</v>
+        <v>2.5291</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0597</v>
+        <v>-1.4149</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2349</v>
+        <v>1.9171</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7803</v>
+        <v>2.2785</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5454</v>
+        <v>-0.3614</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4082</v>
+        <v>3.5826</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7695</v>
+        <v>2.0502</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1778</v>
+        <v>1.5324</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6431</v>
+        <v>-1.6655</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0108</v>
+        <v>0.2283</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6323</v>
+        <v>-1.8938</v>
       </c>
       <c r="P6" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5245</v>
+        <v>-0.4266</v>
       </c>
       <c r="T6" t="n">
-        <v>0.637</v>
+        <v>0.1063</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1125</v>
+        <v>-0.5329</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6076</v>
+        <v>0.7653</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0265</v>
+        <v>0.1354</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6341</v>
+        <v>0.6299</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1294</v>
+        <v>0.3173</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3428</v>
+        <v>1.2509</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4722</v>
+        <v>-0.9336</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9641999999999999</v>
+        <v>0.4636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6966</v>
+        <v>0.3935</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2676</v>
+        <v>0.0701</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0936</v>
+        <v>-0.1463</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6462</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7398</v>
+        <v>-1.0037</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6884</v>
+        <v>-0.3923</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1687</v>
+        <v>-0.1531</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.2392</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9615</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4975</v>
+        <v>2.1444</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. NEDOVIC</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4408</v>
+        <v>0.5809</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0573</v>
+        <v>0.5734</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6166</v>
+        <v>0.0075</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9171</v>
+        <v>-0.2349</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2785</v>
+        <v>-0.7803</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3614</v>
+        <v>0.5454</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5826</v>
+        <v>0.4082</v>
       </c>
       <c r="K8" t="n">
-        <v>2.0502</v>
+        <v>-0.7695</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5324</v>
+        <v>1.1778</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6655</v>
+        <v>-0.6431</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2283</v>
+        <v>-0.0108</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8938</v>
+        <v>-0.6323</v>
       </c>
       <c r="P8" t="n">
         <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1</v>
+        <v>0.1199</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3655</v>
+        <v>0.1652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7345</v>
+        <v>-0.0452</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3851</v>
+        <v>-0.9625</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3818</v>
+        <v>0.2023</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9967</v>
+        <v>-1.1647</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6938</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9913</v>
+        <v>0.6438</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6201</v>
+        <v>0.4406</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3712</v>
+        <v>0.2032</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2223</v>
+        <v>-2.4175</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4121</v>
+        <v>-1.2897</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.6344</v>
+        <v>-1.1278</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2901</v>
+        <v>-4.1287</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.3913</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.8278</v>
+        <v>-3.7374</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.667</v>
+        <v>-1.577</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4775</v>
+        <v>-0.2619</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1445</v>
+        <v>-1.3151</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6231</v>
+        <v>-2.5517</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0602</v>
+        <v>-0.1294</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.6834</v>
+        <v>-2.4223</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>2.7834</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0524</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7027</v>
+        <v>0.2873</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3497</v>
+        <v>-0.2873</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.2166</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2267</v>
+        <v>-4.1659</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2333</v>
+        <v>-0.5315</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-3.6344</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1287</v>
+        <v>-3.2901</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3913</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7374</v>
+        <v>-3.8278</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.577</v>
+        <v>-0.667</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2619</v>
+        <v>0.4775</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3151</v>
+        <v>-1.1445</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5517</v>
+        <v>-2.6231</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1294</v>
+        <v>0.0602</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4223</v>
+        <v>-2.6834</v>
       </c>
       <c r="P11" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8092</v>
+        <v>1.1088</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6563</v>
+        <v>0.7591</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1529</v>
+        <v>0.3497</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.211</v>
+        <v>10.2111</v>
       </c>
       <c r="E12" t="n">
-        <v>13.745</v>
+        <v>13.7451</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5341</v>
+        <v>-3.534</v>
       </c>
       <c r="G12" t="n">
         <v>2.6141</v>
@@ -1360,7 +1360,7 @@
         <v>12.3342</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.719999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>13.2995</v>
@@ -1390,22 +1390,22 @@
         <v>18.5562</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.03960000000000041</v>
+        <v>-0.03959999999999986</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9681</v>
+        <v>1.968</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0076</v>
+        <v>-2.0075</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6778999999999993</v>
+        <v>0.6779000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>10.0751</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.397300000000001</v>
+        <v>-9.3973</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4701</v>
+        <v>4.1612</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9243</v>
+        <v>2.3345</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5458</v>
+        <v>1.8267</v>
       </c>
       <c r="G13" t="n">
         <v>3.0156</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>0.756</v>
+        <v>0.4472</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7591</v>
+        <v>0.1693</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0031</v>
+        <v>0.2779</v>
       </c>
       <c r="V13" t="n">
         <v>0.9304</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6384</v>
+        <v>2.4148</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9997</v>
+        <v>1.1368</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3613</v>
+        <v>1.278</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7141999999999999</v>
+        <v>1.0193</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4131</v>
+        <v>-1.982</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3011</v>
+        <v>3.0013</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0159</v>
+        <v>1.3735</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3669</v>
+        <v>-1.2128</v>
       </c>
       <c r="L14" t="n">
-        <v>0.649</v>
+        <v>2.5863</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7302</v>
+        <v>-0.3542</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.78</v>
+        <v>-0.7692</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9500999999999999</v>
+        <v>0.415</v>
       </c>
       <c r="P14" t="n">
         <v>0.232</v>
@@ -1546,22 +1546,22 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>2.515</v>
+        <v>0.0914</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3239</v>
+        <v>-0.1491</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1911</v>
+        <v>0.2405</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5358</v>
+        <v>2.0976</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3084</v>
+        <v>3.7802</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7726</v>
+        <v>-1.6826</v>
       </c>
       <c r="G15" t="n">
         <v>0.5831</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5834</v>
+        <v>-0.0215</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2434</v>
+        <v>0.2284</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,40 +1657,40 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4997</v>
+        <v>0.7532</v>
       </c>
       <c r="E16" t="n">
-        <v>0.547</v>
+        <v>1.4086</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9527</v>
+        <v>-0.6555</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0193</v>
+        <v>-1.2387</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.982</v>
+        <v>-0.1512</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0013</v>
+        <v>-1.0874</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3735</v>
+        <v>-0.2985</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2128</v>
+        <v>0.5749</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5863</v>
+        <v>-0.8734</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3542</v>
+        <v>-0.9401</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7692</v>
+        <v>-0.7261</v>
       </c>
       <c r="O16" t="n">
-        <v>0.415</v>
+        <v>-0.214</v>
       </c>
       <c r="P16" t="n">
         <v>0.232</v>
@@ -1702,22 +1702,22 @@
         <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8237</v>
+        <v>-0.2427</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7389</v>
+        <v>-0.3497</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0848</v>
+        <v>0.107</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>2.0026</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>3.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1787</v>
+        <v>0.3131</v>
       </c>
       <c r="E17" t="n">
         <v>2.5999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4211</v>
+        <v>-2.2867</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9346</v>
@@ -1780,13 +1780,13 @@
         <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1186</v>
+        <v>0.0158</v>
       </c>
       <c r="T17" t="n">
         <v>0.4208</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5395</v>
+        <v>-0.405</v>
       </c>
       <c r="V17" t="n">
         <v>0.5361</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06759999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9368</v>
+        <v>-0.9329</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8692</v>
+        <v>0.9029</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2387</v>
+        <v>-0.8359</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1512</v>
+        <v>-1.5185</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0874</v>
+        <v>0.6826</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2985</v>
+        <v>-0.6853</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5749</v>
+        <v>-0.6351</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.8734</v>
+        <v>-0.0502</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9401</v>
+        <v>-0.1505</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7261</v>
+        <v>-0.8834</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.214</v>
+        <v>0.7328</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9282</v>
+        <v>-0.1219</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8215</v>
+        <v>-0.2475</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1067</v>
+        <v>0.1256</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0026</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2824</v>
+        <v>-0.0402</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0508</v>
+        <v>1.4663</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7685</v>
+        <v>-1.5065</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8359</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5185</v>
+        <v>-0.4131</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6826</v>
+        <v>-0.3011</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6853</v>
+        <v>1.0159</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6351</v>
+        <v>0.3669</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0502</v>
+        <v>0.649</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1505</v>
+        <v>-1.7302</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8834</v>
+        <v>-0.78</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7328</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3743</v>
+        <v>0.8364</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3655</v>
+        <v>0.7905</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0459</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6421</v>
+        <v>-2.103</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5513</v>
+        <v>1.0231</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1933</v>
+        <v>-3.1261</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3105</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1871</v>
+        <v>0.3519</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0747</v>
+        <v>0.3971</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V21" t="n">
         <v>-2.1444</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.772</v>
+        <v>-2.4518</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0504</v>
+        <v>-1.6966</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7216</v>
+        <v>-0.7552</v>
       </c>
       <c r="G22" t="n">
         <v>0.0417</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4942</v>
+        <v>-0.174</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>-0.0196</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. HOWARD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3482</v>
+        <v>-5.5984</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9204</v>
+        <v>-3.0548</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4278</v>
+        <v>-2.5435</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2798</v>
+        <v>0.0111</v>
       </c>
       <c r="H23" t="n">
-        <v>-6.3719</v>
+        <v>-0.2866</v>
       </c>
       <c r="I23" t="n">
-        <v>4.0921</v>
+        <v>0.2977</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0906</v>
+        <v>1.584</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.5836</v>
+        <v>0.3361</v>
       </c>
       <c r="L23" t="n">
-        <v>4.6742</v>
+        <v>1.2479</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3704</v>
+        <v>-1.5729</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7883</v>
+        <v>-0.6227</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5821</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-3.7112</v>
@@ -2248,28 +2248,28 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>1.715</v>
+        <v>-0.2899</v>
       </c>
       <c r="T23" t="n">
-        <v>1.628</v>
+        <v>0.0002</v>
       </c>
       <c r="U23" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.2902</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. HOWARD</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6707</v>
+        <v>-6.269</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6446</v>
+        <v>-3.864</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0261</v>
+        <v>-2.405</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0111</v>
+        <v>-2.2798</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2866</v>
+        <v>-6.3719</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2977</v>
+        <v>4.0921</v>
       </c>
       <c r="J24" t="n">
-        <v>1.584</v>
+        <v>0.0906</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3361</v>
+        <v>-4.5836</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2479</v>
+        <v>4.6742</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5729</v>
+        <v>-2.3704</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6227</v>
+        <v>-1.7883</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P24" t="n">
         <v>-3.7112</v>
@@ -2326,22 +2326,22 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3623</v>
+        <v>0.7943</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5895</v>
+        <v>0.6844</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1098</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.2111</v>
+        <v>-8.638500000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.534199999999998</v>
+        <v>3.5341</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.7451</v>
+        <v>-12.1726</v>
       </c>
       <c r="G25" t="n">
         <v>-2.613999999999999</v>
@@ -2374,7 +2374,7 @@
         <v>-12.334</v>
       </c>
       <c r="I25" t="n">
-        <v>9.720000000000001</v>
+        <v>9.719999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>10.6856</v>
@@ -2404,16 +2404,16 @@
         <v>11.5977</v>
       </c>
       <c r="S25" t="n">
-        <v>0.03949999999999987</v>
+        <v>1.6123</v>
       </c>
       <c r="T25" t="n">
-        <v>2.0075</v>
+        <v>2.0074</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9681</v>
+        <v>-0.3954000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6778999999999991</v>
       </c>
       <c r="W25" t="n">
         <v>9.397300000000001</v>
